--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
@@ -794,11 +794,6 @@
           <t>126</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 2E, 3, 4A, 4B1, 4B2, 4B3, 4C</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -806,11 +801,6 @@
           <t>127</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -818,11 +808,6 @@
           <t>128</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -830,11 +815,6 @@
           <t>129</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -842,11 +822,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18A, 18B, 1A, 1B, 1C, 2, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -854,11 +829,6 @@
           <t>130</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1, 1A, 1B, 1C, 2, 2A, 2B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -866,11 +836,6 @@
           <t>131</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -878,11 +843,6 @@
           <t>132</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A1, 6A2, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,11 +850,6 @@
           <t>133</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -902,11 +857,6 @@
           <t>134</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A, 6B, 7</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -914,11 +864,6 @@
           <t>135</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -926,11 +871,6 @@
           <t>136</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 2</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -938,11 +878,6 @@
           <t>137</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -950,11 +885,6 @@
           <t>138</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A1, 4A2, 4B1, 4B2, 5A, 5B, 5C, 6A1, 6A2, 6B1, 6B2, 6C1, 6C2, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -962,11 +892,6 @@
           <t>139</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -974,11 +899,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -986,11 +906,6 @@
           <t>140</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B, 3C</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -998,11 +913,6 @@
           <t>141</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11A, 11B1, 11B2, 1A, 1B, 1C, 2, 3, 4A, 4B, 5, 6, 7, 8A, 8B, 8C, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1010,11 +920,6 @@
           <t>142</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1022,11 +927,6 @@
           <t>143</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1034,11 +934,6 @@
           <t>144</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 2A, 2B, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1046,11 +941,6 @@
           <t>145</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B1, 10B2, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1058,11 +948,6 @@
           <t>146</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3, 4A1, 4A2, 4B, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1070,11 +955,6 @@
           <t>147</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A1, 4A2, 4B, 5</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1082,11 +962,6 @@
           <t>148</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3A1, 3A2, 3B, 3C, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1094,11 +969,6 @@
           <t>149</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1106,11 +976,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1118,11 +983,6 @@
           <t>150</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 4C, 4D, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1130,11 +990,6 @@
           <t>151</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1142,11 +997,6 @@
           <t>152</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1154,11 +1004,6 @@
           <t>153</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B, 7C, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1166,11 +1011,6 @@
           <t>154</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B1A, 3B1B, 3B2, 3C, 4A, 4B, 5A, 5B, 6A, 6B, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1178,11 +1018,6 @@
           <t>155</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 2C, 2D, 2E, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B1, 9B2, 9C, 9D</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1190,11 +1025,6 @@
           <t>156</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1202,11 +1032,6 @@
           <t>157</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1214,11 +1039,6 @@
           <t>158</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1226,11 +1046,6 @@
           <t>159</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1238,11 +1053,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1250,11 +1060,6 @@
           <t>160</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A1, 13A2, 13B1, 13B2, 13B3, 13C, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1262,11 +1067,6 @@
           <t>161</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A1A, 6A1B, 6A2, 6B1, 6B2, 7A, 7B1, 7B2, 7B3, 7B4, 7B5, 7C, 7D</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1274,11 +1074,6 @@
           <t>162</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1286,11 +1081,6 @@
           <t>163</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1298,11 +1088,6 @@
           <t>164</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1A1A1, 1A1A2, 1A1B, 1A2, 1B, 2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1310,11 +1095,6 @@
           <t>165</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1322,11 +1102,6 @@
           <t>166</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1334,11 +1109,6 @@
           <t>167</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1, 10, 2A, 2B, 3A1, 3A2, 3B, 3C, 4A, 4B, 4C, 5, 6A, 6B, 7A, 7B, 7C, 7D, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1346,11 +1116,6 @@
           <t>168</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1358,11 +1123,6 @@
           <t>169</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1, 2A, 3</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1370,11 +1130,6 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1382,11 +1137,6 @@
           <t>170</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1394,11 +1144,6 @@
           <t>171</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1406,11 +1151,6 @@
           <t>172</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1418,11 +1158,6 @@
           <t>173</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1430,11 +1165,6 @@
           <t>174</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A1, 17A2, 17A3, 17B1, 17B2, 18, 19, 2, 20, 21, 22A, 22B, 3, 4A, 4B, 4C1, 4C2, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1442,11 +1172,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A1, 16A2, 16A3, 16B1, 16B2, 16B3, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35A, 35B, 36, 37, 38, 39, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1454,11 +1179,6 @@
           <t>176</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1466,11 +1186,6 @@
           <t>177</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12A, 12B, 12C, 13, 14A, 14B, 14C, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1478,11 +1193,6 @@
           <t>178</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4, 5A, 5B1, 5B2, 5C, 6</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1490,11 +1200,6 @@
           <t>179</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1502,11 +1207,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1514,11 +1214,6 @@
           <t>180</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>10, 11, 12A, 12B, 13, 1A, 1B, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1526,11 +1221,6 @@
           <t>181</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1538,11 +1228,6 @@
           <t>182</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A1, 4A2, 4B, 4C1, 4C2</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1550,11 +1235,6 @@
           <t>183</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B1, 1B2, 1B3, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1562,11 +1242,6 @@
           <t>184</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9A, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1574,11 +1249,6 @@
           <t>185</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3A, 3B, 4</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1586,11 +1256,6 @@
           <t>186</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1598,11 +1263,6 @@
           <t>187</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1A3, 1B1, 1B2, 1B3, 2, 3A, 3B, 3C, 4</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1610,11 +1270,6 @@
           <t>188</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1A3, 1B, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1622,11 +1277,6 @@
           <t>189</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 2, 3, 4A, 4B, 4C, 5, 6A, 6B, 6C, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1634,11 +1284,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 4A, 5B, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1646,11 +1291,6 @@
           <t>190</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14A, 14B, 15, 2, 3A, 3B, 4A, 4B, 5, 6A, 6B, 6C, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1658,11 +1298,6 @@
           <t>191</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3A, 3B, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1670,11 +1305,6 @@
           <t>192</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1682,11 +1312,6 @@
           <t>193</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>10, 11, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1694,11 +1319,6 @@
           <t>194</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1706,11 +1326,6 @@
           <t>195</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1718,11 +1333,6 @@
           <t>196</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 4C1, 4C2A, 4C2B, 4D, 4E, 4F, 5A, 5B, 5C, 6A, 6B, 6C, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1730,11 +1340,6 @@
           <t>197</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1742,11 +1347,6 @@
           <t>198</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1754,11 +1354,6 @@
           <t>199</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B, 6</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1766,11 +1361,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1778,11 +1368,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>10, 1A, 1B, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8A, 8B, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1790,11 +1375,6 @@
           <t>200</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1802,11 +1382,6 @@
           <t>201</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1814,11 +1389,6 @@
           <t>202</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1826,11 +1396,6 @@
           <t>203</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C1, 3C2, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1838,11 +1403,6 @@
           <t>204</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1850,11 +1410,6 @@
           <t>205</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1862,11 +1417,6 @@
           <t>206</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1874,11 +1424,6 @@
           <t>207</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1886,11 +1431,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B1A1, 2B1A2, 2B1B, 2B1C, 2B2</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1898,11 +1438,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2A, 2B, 3, 4, 5, 6, 7A1, 7A2, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1910,11 +1445,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 12, 13, 14, 15, 16, 17, 18, 19, 20, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1922,11 +1452,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1934,11 +1459,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 1A, 1B, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1946,11 +1466,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1958,11 +1473,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4A1, 4A2, 4A3, 4A4, 4B, 4C, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1970,11 +1480,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>10, 1A, 1B, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1982,11 +1487,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3A, 3B, 3C, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1994,11 +1494,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>1A, 2, 4</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2006,11 +1501,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2018,11 +1508,6 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 1A, 1B, 2, 3, 4, 5, 6, 7, 8A, 8B, 8C, 8D, 9</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2030,11 +1515,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 7F, 7G</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2042,11 +1522,6 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 15E, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2054,11 +1529,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2066,11 +1536,6 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 2, 20, 21, 22A, 23, 24, 25, 26, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2078,11 +1543,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2A, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2090,11 +1550,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26A, 26B, 27, 28, 29, 3, 30, 31, 32A, 32B, 32C, 32D, 32E, 32F, 32G, 32H, 32I, 32J, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2102,11 +1557,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2114,11 +1564,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2126,11 +1571,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2138,11 +1578,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19A, 19B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2150,11 +1585,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2162,11 +1592,6 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4A, 4B, 5A1, 5A2, 5A3, 5A4, 5B, 5C, 5D</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2174,11 +1599,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8A, 9</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2186,11 +1606,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 1A, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2198,11 +1613,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2210,11 +1620,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21A, 21B, 22, 23, 24, 25, 26A, 26B, 27, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2222,11 +1627,6 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2234,11 +1634,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>10, 11A, 11B, 12A1, 12A2, 12B, 12C, 12D, 13A1A, 13A1B, 13A2, 13B, 13C, 14A1A, 14A1B, 14A2, 14B, 15A, 15B, 15C, 15D, 15E, 16, 1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2246,11 +1641,6 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16A, 16B, 17, 18, 19, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2258,11 +1648,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23, 24, 25A, 25B, 26, 27A, 27B, 28, 29, 3, 30, 31, 32, 33, 34A, 34B, 34C, 35A, 35B, 35C, 35D, 35E, 36, 37, 38, 4, 5, 6, 7, 8A, 8B, 8C, 8D, 8E, 9</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2270,11 +1655,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 2A, 2B, 2C, 2D, 2E, 2F, 3, 4, 5, 6, 7, 8A, 8B, 8C1, 8C2, 8D, 8E, 8F, 9A, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2282,11 +1662,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13A, 13B, 14A, 14B, 15, 16, 17, 18A, 18B, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2294,11 +1669,6 @@
           <t>52</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2306,11 +1676,6 @@
           <t>53</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16A1, 16A2, 16A3, 16A4A, 16A4B, 16B, 17A1, 17A2, 17B, 18, 19A, 19B, 2, 20, 21A, 21B, 22A, 22B, 23A, 23B, 24A, 24B, 25A, 25B, 25C, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2318,11 +1683,6 @@
           <t>54</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2330,11 +1690,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11, 12, 13A1, 13A2, 13B, 14A, 14B, 15A, 15B1, 15B2, 16A, 16B, 16C, 17A, 17B, 17C1, 17C2, 17D, 18, 19A, 19B, 1A, 1B, 1C, 20, 21, 22A, 22B, 23, 24, 25, 26A, 26B, 26C, 26D, 26E, 26F, 26G, 26H, 26I, 27A, 27B, 28A, 28B, 29, 2A, 2B, 30, 31A, 31B, 32A, 32B, 33, 34, 35, 36, 37A, 37B, 37C, 37D, 37E, 37F, 38, 39, 3A, 3B, 3C, 3D, 40, 41, 42, 4A, 4B, 5A, 5B, 6A, 6B, 6C, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2342,11 +1697,6 @@
           <t>56</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 3, 30, 31A, 31B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2354,11 +1704,6 @@
           <t>57</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11A, 11B1, 11B2, 12A, 12B, 13, 14, 15A, 15B, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24A, 24B, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2366,11 +1711,6 @@
           <t>58</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A1, 12A2, 12B, 13, 14A, 14B, 15A, 15B, 15C, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2378,11 +1718,6 @@
           <t>59</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9A, 9B, 9C, 9D, 9E</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2390,11 +1725,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 2A, 2B1, 2B2, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2402,11 +1732,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E1, 1E2, 2A, 2B, 3, 4A1, 4A2, 4A3, 4B, 4C, 5A, 5B, 5C</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2414,11 +1739,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 6C, 6D, 6E, 6F, 6G, 6H, 6I</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2426,11 +1746,6 @@
           <t>62</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6A, 6B, 7, 8, 9A1, 9A2, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2438,11 +1753,6 @@
           <t>63</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2450,11 +1760,6 @@
           <t>64</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>1, 10A1, 10A2, 10A3, 10B, 11, 12, 13A, 13B, 14A, 14B, 15, 16A, 16B, 17, 18A, 18B, 18C, 19A, 19B, 19C, 20, 21, 22, 23, 24A, 24B, 24C, 2A, 2B, 3A, 3B, 4, 5A, 5B, 6, 7, 8A1, 8A2, 8B, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2462,11 +1767,6 @@
           <t>65</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20A, 20B, 21, 22, 23A, 23B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2474,11 +1774,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2486,11 +1781,6 @@
           <t>67</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2498,11 +1788,6 @@
           <t>68</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 16, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2510,11 +1795,6 @@
           <t>69</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>10, 11, 12A, 12B, 12C, 13, 14, 1A, 1B, 1C, 1D, 1E, 2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2522,11 +1802,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13A, 13B, 13C, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20A, 20B, 21, 22, 23, 24, 25A1, 25A2, 25B, 25C, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2534,11 +1809,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 1A, 1B, 1C, 2, 3, 4, 5, 6A1, 6A2A, 6A2B, 6B, 6C, 6D1, 6D2, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2546,11 +1816,6 @@
           <t>71</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3, 4, 5A, 5B, 6, 7A1, 7A2, 7B, 7C1, 7C2, 7C3, 8</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2558,11 +1823,6 @@
           <t>72</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>1, 10, 11A1, 11A2, 11B, 11C, 12, 13, 2A, 2B, 2C, 2D, 3A, 3B, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2570,11 +1830,6 @@
           <t>73</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12A, 12B, 12C, 13A, 13B, 14A, 14B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2582,11 +1837,6 @@
           <t>74</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>1A, 1B1, 1B2, 1B3, 1B4, 1B5, 1B6A, 1B6B, 1B6C, 1B7, 2A, 2B1, 2B2, 2B3, 2B4A, 2B4B, 2B5, 2B6, 2B7, 2B8, 2B9, 2C</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2594,11 +1844,6 @@
           <t>75</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>1A, 1B1, 1B2A1, 1B2A2, 1B2A3, 1B2B, 1B3, 1C, 1D, 2, 3, 4, 5, 6A, 6B</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2606,11 +1851,6 @@
           <t>76</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3, 4, 5A, 5B, 5C, 5D, 5E1, 5E2, 5F, 6, 7, 8A, 8B, 8C, 8D, 8E, 8F, 9</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2618,11 +1858,6 @@
           <t>77</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 8A, 8B, 8C, 9A, 9B, 9C, 9D</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2630,11 +1865,6 @@
           <t>78</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>1, 10, 11A1, 11A2, 11A3, 11B, 11C, 12A, 12B, 13A, 13B, 14, 15A, 15B, 15C, 2, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 9A, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2642,11 +1872,6 @@
           <t>79</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 1C, 2A, 2B, 3, 4A, 4B, 5, 6A, 6B</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2654,11 +1879,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A1, 19, 2, 20A, 20B, 21, 22, 23, 24A, 24B, 25, 26, 3, 31, 32, 33, 34, 35, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2666,11 +1886,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A1, 2A2, 2B, 2C, 2D, 2E, 2F</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2678,11 +1893,6 @@
           <t>81</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 17, 18, 1A, 1B, 2A, 2B, 3, 4A, 4B, 4C, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2690,11 +1900,6 @@
           <t>82</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2702,11 +1907,6 @@
           <t>83</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B1, 7B2, 8A, 8B</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2714,11 +1914,6 @@
           <t>84</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11A, 11B, 11C, 12, 13, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2726,11 +1921,6 @@
           <t>85</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 7C1, 7C2, 7D, 7E, 7F, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2738,11 +1928,6 @@
           <t>86</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2750,11 +1935,6 @@
           <t>87</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>10, 11A, 11B, 12, 13A1, 13A2, 13B, 13C, 14, 15A, 15B, 1A, 1B, 1C, 2, 3, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2762,11 +1942,6 @@
           <t>88</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>10, 1A, 1B, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2774,11 +1949,6 @@
           <t>89</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3A, 3B, 4A1, 4A2, 4A3, 4A4, 4B, 5, 6A, 6B, 6C, 6D, 6E, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2786,11 +1956,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2798,11 +1963,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13A, 13B, 14, 15A1, 15A2, 15B, 15C, 16, 17, 18, 19, 1A1A1A, 1A2, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 20, 21, 22, 23, 24, 25A, 26, 27, 28, 29A, 29B, 2A1, 2A2, 2B, 3, 30, 31A, 32, 33, 34, 35, 36, 37, 38, 4, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2810,11 +1970,6 @@
           <t>91</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4A1, 4A2, 4A3, 4A4, 4B, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2822,11 +1977,6 @@
           <t>92</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22A, 22B, 23, 24, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2834,11 +1984,6 @@
           <t>93</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2846,11 +1991,6 @@
           <t>94</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2858,11 +1998,6 @@
           <t>95</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>10, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2870,11 +2005,6 @@
           <t>96</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2882,11 +2012,6 @@
           <t>97</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B1, 1B2, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2894,21 +2019,11 @@
           <t>98</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>10, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
@@ -794,6 +794,11 @@
           <t>126</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 3, 4A, 4B1, 4B2, 4B3, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -801,6 +806,11 @@
           <t>127</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -808,6 +818,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -815,6 +830,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -822,6 +842,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18A, 18B, 1A, 1B, 1C, 2, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -829,6 +854,11 @@
           <t>130</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1, 1A, 1B, 1C, 2, 2A, 2B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -836,6 +866,11 @@
           <t>131</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -843,6 +878,11 @@
           <t>132</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A1, 6A2, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -850,6 +890,11 @@
           <t>133</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -857,6 +902,11 @@
           <t>134</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -864,6 +914,11 @@
           <t>135</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -871,6 +926,11 @@
           <t>136</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -878,6 +938,11 @@
           <t>137</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -885,6 +950,11 @@
           <t>138</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B1, 4B2, 5A, 5B, 5C, 6A1, 6A2, 6B1, 6B2, 6C1, 6C2, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -892,6 +962,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -899,6 +974,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -906,6 +986,11 @@
           <t>140</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -913,6 +998,11 @@
           <t>141</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A, 11B1, 11B2, 1A, 1B, 1C, 2, 3, 4A, 4B, 5, 6, 7, 8A, 8B, 8C, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -920,6 +1010,11 @@
           <t>142</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -927,6 +1022,11 @@
           <t>143</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -934,6 +1034,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 2A, 2B, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -941,6 +1046,11 @@
           <t>145</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B1, 10B2, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -948,6 +1058,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4A1, 4A2, 4B, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -955,6 +1070,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -962,6 +1082,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A1, 3A2, 3B, 3C, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -969,6 +1094,11 @@
           <t>149</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -976,6 +1106,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -983,6 +1118,11 @@
           <t>150</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -990,6 +1130,11 @@
           <t>151</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -997,6 +1142,11 @@
           <t>152</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1004,6 +1154,11 @@
           <t>153</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B, 7C, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1011,6 +1166,11 @@
           <t>154</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B1A, 3B1B, 3B2, 3C, 4A, 4B, 5A, 5B, 6A, 6B, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1018,6 +1178,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 2C, 2D, 2E, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B1, 9B2, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1025,6 +1190,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1032,6 +1202,11 @@
           <t>157</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1039,6 +1214,11 @@
           <t>158</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1046,6 +1226,11 @@
           <t>159</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1053,6 +1238,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1060,6 +1250,11 @@
           <t>160</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A1, 13A2, 13B1, 13B2, 13B3, 13C, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1067,6 +1262,11 @@
           <t>161</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A1A, 6A1B, 6A2, 6B1, 6B2, 7A, 7B1, 7B2, 7B3, 7B4, 7B5, 7C, 7D</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1074,6 +1274,11 @@
           <t>162</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1081,6 +1286,11 @@
           <t>163</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1088,6 +1298,11 @@
           <t>164</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1A1A1, 1A1A2, 1A1B, 1A2, 1B, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1095,6 +1310,11 @@
           <t>165</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1102,6 +1322,11 @@
           <t>166</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1109,6 +1334,11 @@
           <t>167</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 3A1, 3A2, 3B, 3C, 4A, 4B, 4C, 5, 6A, 6B, 7A, 7B, 7C, 7D, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1116,6 +1346,11 @@
           <t>168</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1123,6 +1358,11 @@
           <t>169</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1, 2A, 3</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1130,6 +1370,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1137,6 +1382,11 @@
           <t>170</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1144,6 +1394,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1151,6 +1406,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1158,6 +1418,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1165,6 +1430,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A1, 17A2, 17A3, 17B1, 17B2, 18, 19, 2, 20, 21, 22A, 22B, 3, 4A, 4B, 4C1, 4C2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1172,6 +1442,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A1, 16A2, 16A3, 16B1, 16B2, 16B3, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35A, 35B, 36, 37, 38, 39, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1179,6 +1454,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1186,6 +1466,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12A, 12B, 12C, 13, 14A, 14B, 14C, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1193,6 +1478,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5A, 5B1, 5B2, 5C, 6</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1200,6 +1490,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1207,6 +1502,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1214,6 +1514,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13, 1A, 1B, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1221,6 +1526,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1228,6 +1538,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B, 4C1, 4C2</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1235,6 +1550,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1B3, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1242,6 +1562,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1249,6 +1574,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1256,6 +1586,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1263,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B1, 1B2, 1B3, 2, 3A, 3B, 3C, 4</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1270,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1277,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4A, 4B, 4C, 5, 6A, 6B, 6C, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1284,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 4A, 5B, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1291,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14A, 14B, 15, 2, 3A, 3B, 4A, 4B, 5, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1298,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1305,6 +1670,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1312,6 +1682,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1319,6 +1694,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1326,6 +1706,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1333,6 +1718,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C1, 4C2A, 4C2B, 4D, 4E, 4F, 5A, 5B, 5C, 6A, 6B, 6C, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1340,6 +1730,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1347,6 +1742,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1354,6 +1754,11 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1361,6 +1766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1368,6 +1778,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1375,6 +1790,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1382,6 +1802,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1389,6 +1814,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1396,6 +1826,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C1, 3C2, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1403,6 +1838,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1410,6 +1850,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1417,6 +1862,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1424,6 +1874,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1431,11 +1886,21 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A1, 2B1A2, 2B1B, 2B1C, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
           <t>22</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2A, 2B, 3, 4, 5, 6, 7A1, 7A2, 7B, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
@@ -1598,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B1, 1B2, 1B3, 2, 3A, 3B, 3C, 4</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1605,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1612,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4A, 4B, 4C, 5, 6A, 6B, 6C, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1619,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 4A, 5B, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1626,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14A, 14B, 15, 2, 3A, 3B, 4A, 4B, 5, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1633,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1640,6 +1670,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1647,6 +1682,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1654,6 +1694,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1661,6 +1706,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1668,6 +1718,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C1, 4C2A, 4C2B, 4D, 4E, 4F, 5A, 5B, 5C, 6A, 6B, 6C, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1675,6 +1730,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1682,6 +1742,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1689,6 +1754,11 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1696,6 +1766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1703,6 +1778,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1710,6 +1790,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1717,6 +1802,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1724,6 +1814,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1731,6 +1826,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C1, 3C2, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1738,6 +1838,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1745,6 +1850,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1752,6 +1862,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1759,6 +1874,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1766,6 +1886,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A1, 2B1A2, 2B1B, 2B1C, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1773,6 +1898,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2A, 2B, 3, 4, 5, 6, 7A1, 7A2, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1780,6 +1910,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 12, 13, 14, 15, 16, 17, 18, 19, 20, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1787,6 +1922,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1794,6 +1934,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1801,6 +1946,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1808,6 +1958,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A1, 4A2, 4A3, 4A4, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1815,6 +1970,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1822,6 +1982,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 3C, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1829,6 +1994,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1A, 2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1836,6 +2006,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1843,6 +2018,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 1A, 1B, 2, 3, 4, 5, 6, 7, 8A, 8B, 8C, 8D, 9</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1850,6 +2030,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 7F, 7G</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1857,6 +2042,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 15E, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1864,6 +2054,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1871,6 +2066,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 2, 20, 21, 22A, 23, 24, 25, 26, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1878,6 +2078,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2A, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1885,6 +2090,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26A, 26B, 27, 28, 29, 3, 30, 31, 32A, 32B, 32C, 32D, 32E, 32F, 32G, 32H, 32I, 32J, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1892,6 +2102,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1899,6 +2114,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1906,6 +2126,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1913,6 +2138,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19A, 19B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1920,6 +2150,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1927,6 +2162,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5A1, 5A2, 5A3, 5A4, 5B, 5C, 5D</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1934,6 +2174,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8A, 9</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1941,6 +2186,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1948,6 +2198,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1955,6 +2210,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21A, 21B, 22, 23, 24, 25, 26A, 26B, 27, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1962,6 +2222,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1969,6 +2234,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12A1, 12A2, 12B, 12C, 12D, 13A1A, 13A1B, 13A2, 13B, 13C, 14A1A, 14A1B, 14A2, 14B, 15A, 15B, 15C, 15D, 15E, 16, 1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1976,6 +2246,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16A, 16B, 17, 18, 19, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1983,6 +2258,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23, 24, 25A, 25B, 26, 27A, 27B, 28, 29, 3, 30, 31, 32, 33, 34A, 34B, 34C, 35A, 35B, 35C, 35D, 35E, 36, 37, 38, 4, 5, 6, 7, 8A, 8B, 8C, 8D, 8E, 9</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1990,6 +2270,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 2A, 2B, 2C, 2D, 2E, 2F, 3, 4, 5, 6, 7, 8A, 8B, 8C1, 8C2, 8D, 8E, 8F, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1997,6 +2282,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13A, 13B, 14A, 14B, 15, 16, 17, 18A, 18B, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2004,6 +2294,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2011,6 +2306,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16A1, 16A2, 16A3, 16A4A, 16A4B, 16B, 17A1, 17A2, 17B, 18, 19A, 19B, 2, 20, 21A, 21B, 22A, 22B, 23A, 23B, 24A, 24B, 25A, 25B, 25C, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2018,6 +2318,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2025,6 +2330,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13A1, 13A2, 13B, 14A, 14B, 15A, 15B1, 15B2, 16A, 16B, 16C, 17A, 17B, 17C1, 17C2, 17D, 18, 19A, 19B, 1A, 1B, 1C, 20, 21, 22A, 22B, 23, 24, 25, 26A, 26B, 26C, 26D, 26E, 26F, 26G, 26H, 26I, 27A, 27B, 28A, 28B, 29, 2A, 2B, 30, 31A, 31B, 32A, 32B, 33, 34, 35, 36, 37A, 37B, 37C, 37D, 37E, 37F, 38, 39, 3A, 3B, 3C, 3D, 40, 41, 42, 4A, 4B, 5A, 5B, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2032,6 +2342,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 3, 30, 31A, 31B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2039,6 +2354,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A, 11B1, 11B2, 12A, 12B, 13, 14, 15A, 15B, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24A, 24B, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2046,6 +2366,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A1, 12A2, 12B, 13, 14A, 14B, 15A, 15B, 15C, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2053,6 +2378,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9A, 9B, 9C, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2060,6 +2390,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 2A, 2B1, 2B2, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2067,6 +2402,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E1, 1E2, 2A, 2B, 3, 4A1, 4A2, 4A3, 4B, 4C, 5A, 5B, 5C</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2074,6 +2414,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 6C, 6D, 6E, 6F, 6G, 6H, 6I</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2081,6 +2426,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6A, 6B, 7, 8, 9A1, 9A2, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2088,6 +2438,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2095,6 +2450,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1, 10A1, 10A2, 10A3, 10B, 11, 12, 13A, 13B, 14A, 14B, 15, 16A, 16B, 17, 18A, 18B, 18C, 19A, 19B, 19C, 20, 21, 22, 23, 24A, 24B, 24C, 2A, 2B, 3A, 3B, 4, 5A, 5B, 6, 7, 8A1, 8A2, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2102,6 +2462,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20A, 20B, 21, 22, 23A, 23B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2109,6 +2474,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2116,6 +2486,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2123,6 +2498,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 16, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2130,6 +2510,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 12C, 13, 14, 1A, 1B, 1C, 1D, 1E, 2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2137,6 +2522,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 13C, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20A, 20B, 21, 22, 23, 24, 25A1, 25A2, 25B, 25C, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2144,6 +2534,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 1C, 2, 3, 4, 5, 6A1, 6A2A, 6A2B, 6B, 6C, 6D1, 6D2, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2151,6 +2546,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3, 4, 5A, 5B, 6, 7A1, 7A2, 7B, 7C1, 7C2, 7C3, 8</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2158,6 +2558,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 10, 11A1, 11A2, 11B, 11C, 12, 13, 2A, 2B, 2C, 2D, 3A, 3B, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2165,6 +2570,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12A, 12B, 12C, 13A, 13B, 14A, 14B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2172,6 +2582,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1B3, 1B4, 1B5, 1B6A, 1B6B, 1B6C, 1B7, 2A, 2B1, 2B2, 2B3, 2B4A, 2B4B, 2B5, 2B6, 2B7, 2B8, 2B9, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2179,6 +2594,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2A1, 1B2A2, 1B2A3, 1B2B, 1B3, 1C, 1D, 2, 3, 4, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2186,6 +2606,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5A, 5B, 5C, 5D, 5E1, 5E2, 5F, 6, 7, 8A, 8B, 8C, 8D, 8E, 8F, 9</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2193,6 +2618,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 8A, 8B, 8C, 9A, 9B, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2200,6 +2630,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1, 10, 11A1, 11A2, 11A3, 11B, 11C, 12A, 12B, 13A, 13B, 14, 15A, 15B, 15C, 2, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2207,6 +2642,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2A, 2B, 3, 4A, 4B, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2214,6 +2654,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A1, 19, 2, 20A, 20B, 21, 22, 23, 24A, 24B, 25, 26, 3, 31, 32, 33, 34, 35, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2221,6 +2666,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A1, 2A2, 2B, 2C, 2D, 2E, 2F</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2228,6 +2678,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 17, 18, 1A, 1B, 2A, 2B, 3, 4A, 4B, 4C, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2235,6 +2690,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2242,6 +2702,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B1, 7B2, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2249,6 +2714,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A, 11B, 11C, 12, 13, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2256,6 +2726,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 7C1, 7C2, 7D, 7E, 7F, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2263,6 +2738,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2270,6 +2750,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13A1, 13A2, 13B, 13C, 14, 15A, 15B, 1A, 1B, 1C, 2, 3, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2277,6 +2762,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2284,6 +2774,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3A, 3B, 4A1, 4A2, 4A3, 4A4, 4B, 5, 6A, 6B, 6C, 6D, 6E, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2291,6 +2786,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2298,6 +2798,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14, 15A1, 15A2, 15B, 15C, 16, 17, 18, 19, 1A1A1A, 1A2, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 20, 21, 22, 23, 24, 25A, 26, 27, 28, 29A, 29B, 2A1, 2A2, 2B, 3, 30, 31A, 32, 33, 34, 35, 36, 37, 38, 4, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2305,6 +2810,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A1, 4A2, 4A3, 4A4, 4B, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2312,11 +2822,21 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22A, 22B, 23, 24, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
           <t>93</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
@@ -2846,6 +2846,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2853,6 +2858,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2860,6 +2870,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2867,6 +2882,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2874,11 +2894,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Panchalai_13.401025_80.017544.xlsx
@@ -1910,6 +1910,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 12, 13, 14, 15, 16, 17, 18, 19, 20, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1917,6 +1922,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1924,6 +1934,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1931,6 +1946,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1938,6 +1958,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A1, 4A2, 4A3, 4A4, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1945,6 +1970,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1952,6 +1982,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 3C, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1959,6 +1994,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1A, 2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1966,6 +2006,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1973,6 +2018,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 1A, 1B, 2, 3, 4, 5, 6, 7, 8A, 8B, 8C, 8D, 9</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1980,6 +2030,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 7E, 7F, 7G</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1987,6 +2042,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 15D, 15E, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1994,6 +2054,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2001,6 +2066,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 2, 20, 21, 22A, 23, 24, 25, 26, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2008,6 +2078,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2A, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2015,6 +2090,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26A, 26B, 27, 28, 29, 3, 30, 31, 32A, 32B, 32C, 32D, 32E, 32F, 32G, 32H, 32I, 32J, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2022,6 +2102,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2029,6 +2114,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2036,6 +2126,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2043,6 +2138,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19A, 19B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2050,6 +2150,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2057,6 +2162,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5A1, 5A2, 5A3, 5A4, 5B, 5C, 5D</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2064,6 +2174,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8A, 9</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2071,6 +2186,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2078,6 +2198,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2085,6 +2210,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 2, 20, 21A, 21B, 22, 23, 24, 25, 26A, 26B, 27, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2092,6 +2222,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2099,6 +2234,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12A1, 12A2, 12B, 12C, 12D, 13A1A, 13A1B, 13A2, 13B, 13C, 14A1A, 14A1B, 14A2, 14B, 15A, 15B, 15C, 15D, 15E, 16, 1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2106,6 +2246,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16A, 16B, 17, 18, 19, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2113,6 +2258,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23, 24, 25A, 25B, 26, 27A, 27B, 28, 29, 3, 30, 31, 32, 33, 34A, 34B, 34C, 35A, 35B, 35C, 35D, 35E, 36, 37, 38, 4, 5, 6, 7, 8A, 8B, 8C, 8D, 8E, 9</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2120,6 +2270,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 2A, 2B, 2C, 2D, 2E, 2F, 3, 4, 5, 6, 7, 8A, 8B, 8C1, 8C2, 8D, 8E, 8F, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2127,6 +2282,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13A, 13B, 14A, 14B, 15, 16, 17, 18A, 18B, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2134,6 +2294,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2141,6 +2306,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16A1, 16A2, 16A3, 16A4A, 16A4B, 16B, 17A1, 17A2, 17B, 18, 19A, 19B, 2, 20, 21A, 21B, 22A, 22B, 23A, 23B, 24A, 24B, 25A, 25B, 25C, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2148,6 +2318,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2155,6 +2330,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13A1, 13A2, 13B, 14A, 14B, 15A, 15B1, 15B2, 16A, 16B, 16C, 17A, 17B, 17C1, 17C2, 17D, 18, 19A, 19B, 1A, 1B, 1C, 20, 21, 22A, 22B, 23, 24, 25, 26A, 26B, 26C, 26D, 26E, 26F, 26G, 26H, 26I, 27A, 27B, 28A, 28B, 29, 2A, 2B, 30, 31A, 31B, 32A, 32B, 33, 34, 35, 36, 37A, 37B, 37C, 37D, 37E, 37F, 38, 39, 3A, 3B, 3C, 3D, 40, 41, 42, 4A, 4B, 5A, 5B, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2162,6 +2342,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 3, 30, 31A, 31B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2169,6 +2354,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A, 11B1, 11B2, 12A, 12B, 13, 14, 15A, 15B, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24A, 24B, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2176,6 +2366,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A1, 12A2, 12B, 13, 14A, 14B, 15A, 15B, 15C, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2183,6 +2378,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 3, 4, 5, 6, 7, 8, 9A, 9B, 9C, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2190,6 +2390,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 2A, 2B1, 2B2, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2197,6 +2402,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E1, 1E2, 2A, 2B, 3, 4A1, 4A2, 4A3, 4B, 4C, 5A, 5B, 5C</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2204,6 +2414,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 6C, 6D, 6E, 6F, 6G, 6H, 6I</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2211,6 +2426,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6A, 6B, 7, 8, 9A1, 9A2, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2218,6 +2438,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2225,6 +2450,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1, 10A1, 10A2, 10A3, 10B, 11, 12, 13A, 13B, 14A, 14B, 15, 16A, 16B, 17, 18A, 18B, 18C, 19A, 19B, 19C, 20, 21, 22, 23, 24A, 24B, 24C, 2A, 2B, 3A, 3B, 4, 5A, 5B, 6, 7, 8A1, 8A2, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2232,6 +2462,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20A, 20B, 21, 22, 23A, 23B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2239,6 +2474,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2246,6 +2486,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2253,6 +2498,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 15C, 16, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2260,6 +2510,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 12C, 13, 14, 1A, 1B, 1C, 1D, 1E, 2, 3A, 3B, 4, 5A, 5B, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2267,6 +2522,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 13C, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20A, 20B, 21, 22, 23, 24, 25A1, 25A2, 25B, 25C, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2274,6 +2534,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 1C, 2, 3, 4, 5, 6A1, 6A2A, 6A2B, 6B, 6C, 6D1, 6D2, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2281,6 +2546,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3, 4, 5A, 5B, 6, 7A1, 7A2, 7B, 7C1, 7C2, 7C3, 8</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2288,6 +2558,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 10, 11A1, 11A2, 11B, 11C, 12, 13, 2A, 2B, 2C, 2D, 3A, 3B, 4A, 4B, 5A, 5B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2295,6 +2570,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12A, 12B, 12C, 13A, 13B, 14A, 14B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2302,6 +2582,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1B3, 1B4, 1B5, 1B6A, 1B6B, 1B6C, 1B7, 2A, 2B1, 2B2, 2B3, 2B4A, 2B4B, 2B5, 2B6, 2B7, 2B8, 2B9, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2309,6 +2594,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2A1, 1B2A2, 1B2A3, 1B2B, 1B3, 1C, 1D, 2, 3, 4, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2316,6 +2606,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5A, 5B, 5C, 5D, 5E1, 5E2, 5F, 6, 7, 8A, 8B, 8C, 8D, 8E, 8F, 9</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2323,6 +2618,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 8A, 8B, 8C, 9A, 9B, 9C, 9D</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2330,6 +2630,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1, 10, 11A1, 11A2, 11A3, 11B, 11C, 12A, 12B, 13A, 13B, 14, 15A, 15B, 15C, 2, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2337,6 +2642,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2A, 2B, 3, 4A, 4B, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2344,6 +2654,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A1, 19, 2, 20A, 20B, 21, 22, 23, 24A, 24B, 25, 26, 3, 31, 32, 33, 34, 35, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2351,6 +2666,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A1, 2A2, 2B, 2C, 2D, 2E, 2F</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2358,6 +2678,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16A, 16B, 17, 18, 1A, 1B, 2A, 2B, 3, 4A, 4B, 4C, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2365,6 +2690,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2372,6 +2702,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B1, 7B2, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2379,6 +2714,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A, 11B, 11C, 12, 13, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2386,6 +2726,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 7A, 7B, 7C1, 7C2, 7D, 7E, 7F, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2393,6 +2738,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2400,6 +2750,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13A1, 13A2, 13B, 13C, 14, 15A, 15B, 1A, 1B, 1C, 2, 3, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2407,6 +2762,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4, 5, 6A, 6B, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2414,6 +2774,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3A, 3B, 4A1, 4A2, 4A3, 4A4, 4B, 5, 6A, 6B, 6C, 6D, 6E, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2421,6 +2786,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2428,6 +2798,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14, 15A1, 15A2, 15B, 15C, 16, 17, 18, 19, 1A1A1A, 1A2, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 20, 21, 22, 23, 24, 25A, 26, 27, 28, 29A, 29B, 2A1, 2A2, 2B, 3, 30, 31A, 32, 33, 34, 35, 36, 37, 38, 4, 5A, 5B, 5C, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2435,6 +2810,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A1, 4A2, 4A3, 4A4, 4B, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2442,6 +2822,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22A, 22B, 23, 24, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2449,6 +2834,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2456,6 +2846,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2463,6 +2858,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2470,6 +2870,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2477,6 +2882,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2484,11 +2894,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>
